--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/02. Trả bảo hành/TBH_AnhTuanNB_140726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/02. Trả bảo hành/TBH_AnhTuanNB_140726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFB849A-4367-4AA7-881E-001A50BD5BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37E7B4C-764E-45BE-90B1-6089F4830D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="P.TraBaoHanh" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">P.TraBaoHanh!$A$1:$I$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">P.TraBaoHanh!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -164,6 +164,18 @@
   </si>
   <si>
     <t>ĐL. Nam Anh</t>
+  </si>
+  <si>
+    <t>00BD000CDF</t>
+  </si>
+  <si>
+    <t>SIM + ổ cứng</t>
+  </si>
+  <si>
+    <t>Treo không khởi động được, chạm nguồn 3v3</t>
+  </si>
+  <si>
+    <t>Không sửa được</t>
   </si>
 </sst>
 </file>
@@ -299,7 +311,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -312,8 +324,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -466,6 +484,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -474,7 +505,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -580,6 +611,39 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -613,37 +677,19 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1009,7 +1055,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="5" customWidth="1"/>
@@ -1027,77 +1073,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54"/>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="55" t="s">
+      <c r="A1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="56" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="58"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="47"/>
     </row>
     <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="59" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="61"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="50"/>
     </row>
     <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="62" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="64"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="53"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
       <c r="E6" s="28"/>
       <c r="F6" s="29"/>
       <c r="G6" s="29"/>
@@ -1107,12 +1153,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
       <c r="E7" s="28"/>
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
@@ -1120,12 +1166,12 @@
       <c r="I7" s="30"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
       <c r="E8" s="28"/>
       <c r="F8" s="29"/>
       <c r="G8" s="29"/>
@@ -1133,12 +1179,12 @@
       <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
       <c r="E9" s="28"/>
       <c r="F9" s="29"/>
       <c r="G9" s="29"/>
@@ -1190,10 +1236,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="26"/>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="67" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="27">
@@ -1201,33 +1247,35 @@
       </c>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25">
         <v>2</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="26"/>
+        <v>47</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>48</v>
+      </c>
       <c r="E12" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="27"/>
+      <c r="G12" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="66"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="25">
         <v>3</v>
       </c>
@@ -1235,23 +1283,25 @@
         <v>22</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>34</v>
+      <c r="F13" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="68" t="s">
+        <v>31</v>
       </c>
       <c r="I13" s="27"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25">
         <v>4</v>
       </c>
@@ -1259,20 +1309,18 @@
         <v>22</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="26" t="s">
-        <v>38</v>
-      </c>
+      <c r="F14" s="26"/>
       <c r="G14" s="26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I14" s="27"/>
       <c r="J14" s="7"/>
@@ -1285,17 +1333,17 @@
         <v>22</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="26" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>41</v>
+        <v>38</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>36</v>
       </c>
       <c r="H15" s="26" t="s">
         <v>37</v>
@@ -1303,112 +1351,127 @@
       <c r="I15" s="27"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25">
         <v>6</v>
       </c>
       <c r="B16" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="41" t="s">
-        <v>42</v>
+      <c r="C16" s="26" t="s">
+        <v>39</v>
       </c>
       <c r="D16" s="26"/>
       <c r="E16" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26" t="s">
+      <c r="F16" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="27"/>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25">
+        <v>7</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="H17" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I17" s="27">
         <v>260000</v>
       </c>
-      <c r="J16" s="7"/>
-    </row>
-    <row r="17" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="51" t="s">
+      <c r="J17" s="7"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="40">
-        <f>SUM(I11:I16)</f>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="40">
+        <f>SUM(I11:I17)</f>
         <v>610000</v>
       </c>
-      <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="9"/>
       <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
-      <c r="I19" s="20"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="50" t="s">
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-    </row>
-    <row r="21" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48" t="s">
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="48" t="s">
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-    </row>
-    <row r="22" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="9"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
     </row>
     <row r="23" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22"/>
@@ -1416,7 +1479,7 @@
       <c r="C23" s="14"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="6"/>
+      <c r="F23" s="13"/>
       <c r="G23" s="23"/>
       <c r="H23" s="8"/>
       <c r="I23" s="9"/>
@@ -1433,67 +1496,78 @@
       <c r="I24" s="9"/>
     </row>
     <row r="25" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="16"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="9"/>
     </row>
     <row r="26" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="21"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="16"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="49" t="s">
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-    </row>
-    <row r="27" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="18"/>
-    </row>
-    <row r="29" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-    </row>
-    <row r="68" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="18"/>
+    </row>
+    <row r="30" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+    </row>
+    <row r="69" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="D3:I3"/>
     <mergeCell ref="D4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="98" orientation="landscape" r:id="rId1"/>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/02. Trả bảo hành/TBH_AnhTuanNB_140726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/02. Trả bảo hành/TBH_AnhTuanNB_140726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37E7B4C-764E-45BE-90B1-6089F4830D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CCA967-50A7-4E17-8A88-3CDAC9C1028A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -611,6 +611,54 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -642,54 +690,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1073,77 +1073,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43"/>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="44" t="s">
+      <c r="A1" s="59"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="45" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="47"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="48" t="s">
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="50"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="51" t="s">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="53"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="69"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="28"/>
       <c r="F6" s="29"/>
       <c r="G6" s="29"/>
@@ -1153,12 +1153,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="28"/>
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
@@ -1166,12 +1166,12 @@
       <c r="I7" s="30"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="28"/>
       <c r="F8" s="29"/>
       <c r="G8" s="29"/>
@@ -1179,12 +1179,12 @@
       <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="28"/>
       <c r="F9" s="29"/>
       <c r="G9" s="29"/>
@@ -1236,10 +1236,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="26"/>
-      <c r="G11" s="67" t="s">
+      <c r="G11" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="67" t="s">
+      <c r="H11" s="45" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="27">
@@ -1263,16 +1263,16 @@
       <c r="E12" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="65" t="s">
+      <c r="F12" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="69" t="s">
+      <c r="G12" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="69" t="s">
+      <c r="H12" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="66"/>
+      <c r="I12" s="44"/>
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1292,10 +1292,10 @@
       <c r="F13" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="68" t="s">
+      <c r="H13" s="46" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="27"/>
@@ -1404,16 +1404,16 @@
       <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="64"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="40">
         <f>SUM(I11:I17)</f>
         <v>610000</v>
@@ -1444,34 +1444,34 @@
       <c r="I20" s="20"/>
     </row>
     <row r="21" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
       <c r="E21" s="32"/>
       <c r="F21" s="33"/>
-      <c r="G21" s="61" t="s">
+      <c r="G21" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
     </row>
     <row r="22" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35"/>
-      <c r="G22" s="59" t="s">
+      <c r="G22" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
     </row>
     <row r="23" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22"/>
@@ -1518,19 +1518,19 @@
       <c r="I26" s="16"/>
     </row>
     <row r="27" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
       <c r="E27" s="36"/>
       <c r="F27" s="37"/>
-      <c r="G27" s="60" t="s">
+      <c r="G27" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
     </row>
     <row r="28" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
@@ -1544,12 +1544,17 @@
       <c r="I28" s="18"/>
     </row>
     <row r="30" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B30" s="56"/>
-      <c r="C30" s="56"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
     </row>
     <row r="69" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A6:D6"/>
@@ -1563,11 +1568,6 @@
     <mergeCell ref="G22:I22"/>
     <mergeCell ref="G27:I27"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="98" orientation="landscape" r:id="rId1"/>
